--- a/tabtools/demo/regtab.xlsx
+++ b/tabtools/demo/regtab.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="250" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="330" uniqueCount="46">
   <si>
     <t>Table 2. OLS Regression</t>
   </si>
@@ -158,1593 +158,3223 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1185">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
+  <fonts count="1565">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -5256,7 +6886,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="895">
+  <borders count="1182">
     <border>
       <left/>
       <right/>
@@ -11366,11 +12996,1972 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="895">
+  <cellXfs count="1182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -14867,6 +18458,1130 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="1184" fillId="0" borderId="894" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="895" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="896" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="897" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="898" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="899" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="900" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="901" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="902" xfId="0"/>
+    <xf numFmtId="0" fontId="1185" fillId="0" borderId="903" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1186" fillId="0" borderId="904" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1187" fillId="0" borderId="905" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1188" fillId="0" borderId="906" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1189" fillId="0" borderId="907" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1190" fillId="0" borderId="908" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1192" fillId="0" borderId="909" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1194" fillId="0" borderId="910" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1196" fillId="0" borderId="911" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1197" fillId="0" borderId="912" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1198" fillId="0" borderId="913" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1199" fillId="0" borderId="914" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1200" fillId="0" borderId="915" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1201" fillId="0" borderId="916" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1202" fillId="0" borderId="917" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1203" fillId="0" borderId="918" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1204" fillId="0" borderId="919" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1205" fillId="0" borderId="920" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1206" fillId="0" borderId="921" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1207" fillId="0" borderId="922" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1208" fillId="0" borderId="923" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1209" fillId="0" borderId="924" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1210" fillId="0" borderId="925" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1211" fillId="0" borderId="926" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1212" fillId="0" borderId="927" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1213" fillId="0" borderId="928" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1214" fillId="0" borderId="929" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1216" fillId="0" borderId="930" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1218" fillId="0" borderId="931" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1220" fillId="0" borderId="932" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1221" fillId="0" borderId="933" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1222" fillId="0" borderId="934" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1223" fillId="0" borderId="935" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1224" fillId="0" borderId="936" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1225" fillId="0" borderId="937" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1226" fillId="0" borderId="938" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1227" fillId="0" borderId="939" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1228" fillId="0" borderId="940" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1229" fillId="0" borderId="941" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1230" fillId="0" borderId="942" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1231" fillId="0" borderId="943" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1232" fillId="0" borderId="944" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1233" fillId="0" borderId="945" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1234" fillId="0" borderId="946" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1235" fillId="0" borderId="947" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1236" fillId="0" borderId="948" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1237" fillId="0" borderId="949" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1238" fillId="0" borderId="950" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1239" fillId="0" borderId="951" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1240" fillId="0" borderId="952" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1241" fillId="0" borderId="953" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1242" fillId="0" borderId="954" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1243" fillId="0" borderId="955" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1244" fillId="0" borderId="956" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1245" fillId="0" borderId="957" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1246" fillId="0" borderId="958" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1247" fillId="0" borderId="959" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1248" fillId="0" borderId="960" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1250" fillId="0" borderId="961" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1252" fillId="0" borderId="962" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1254" fillId="0" borderId="963" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1256" fillId="0" borderId="964" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1258" fillId="0" borderId="965" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1260" fillId="0" borderId="966" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1262" fillId="0" borderId="967" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1264" fillId="0" borderId="968" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1265" fillId="0" borderId="969" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1266" fillId="0" borderId="970" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1267" fillId="0" borderId="971" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1268" fillId="0" borderId="972" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1269" fillId="0" borderId="973" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1270" fillId="0" borderId="974" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1271" fillId="0" borderId="975" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1272" fillId="0" borderId="976" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1273" fillId="0" borderId="977" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1274" fillId="0" borderId="978" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1275" fillId="0" borderId="979" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1276" fillId="0" borderId="980" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1277" fillId="0" borderId="981" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1278" fillId="0" borderId="982" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1279" fillId="0" borderId="983" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1280" fillId="0" borderId="984" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1281" fillId="0" borderId="985" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1282" fillId="0" borderId="986" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1283" fillId="0" borderId="987" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1284" fillId="0" borderId="988" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1285" fillId="0" borderId="989" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1286" fillId="0" borderId="990" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1288" fillId="0" borderId="991" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1290" fillId="0" borderId="992" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1292" fillId="0" borderId="993" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1294" fillId="0" borderId="994" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1296" fillId="0" borderId="995" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1298" fillId="0" borderId="996" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1300" fillId="0" borderId="997" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1301" fillId="0" borderId="998" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1302" fillId="0" borderId="999" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1303" fillId="0" borderId="1000" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1304" fillId="0" borderId="1001" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1305" fillId="0" borderId="1002" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1306" fillId="0" borderId="1003" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1307" fillId="0" borderId="1004" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1308" fillId="0" borderId="1005" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1309" fillId="0" borderId="1006" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1310" fillId="0" borderId="1007" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1311" fillId="0" borderId="1008" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1312" fillId="0" borderId="1009" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1313" fillId="0" borderId="1010" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1314" fillId="0" borderId="1011" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1315" fillId="0" borderId="1012" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1316" fillId="0" borderId="1013" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1317" fillId="0" borderId="1014" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1318" fillId="0" borderId="1015" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1319" fillId="0" borderId="1016" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1320" fillId="0" borderId="1017" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1321" fillId="0" borderId="1018" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1322" fillId="0" borderId="1019" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1323" fillId="0" borderId="1020" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1324" fillId="0" borderId="1021" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1325" fillId="0" borderId="1022" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1326" fillId="0" borderId="1023" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1327" fillId="0" borderId="1024" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1328" fillId="0" borderId="1025" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1329" fillId="0" borderId="1026" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1330" fillId="0" borderId="1027" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1331" fillId="0" borderId="1028" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1332" fillId="0" borderId="1029" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1333" fillId="0" borderId="1030" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1334" fillId="0" borderId="1031" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1335" fillId="0" borderId="1032" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1336" fillId="0" borderId="1033" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1337" fillId="0" borderId="1034" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1338" fillId="0" borderId="1035" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1339" fillId="0" borderId="1036" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1340" fillId="0" borderId="1037" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1341" fillId="0" borderId="1038" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1342" fillId="0" borderId="1039" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1343" fillId="0" borderId="1040" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1344" fillId="0" borderId="1041" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1345" fillId="0" borderId="1042" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1346" fillId="0" borderId="1043" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1347" fillId="0" borderId="1044" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1348" fillId="0" borderId="1045" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1349" fillId="0" borderId="1046" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1350" fillId="0" borderId="1047" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1351" fillId="0" borderId="1048" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1352" fillId="0" borderId="1049" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1353" fillId="0" borderId="1050" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1354" fillId="0" borderId="1051" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1355" fillId="0" borderId="1052" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1356" fillId="0" borderId="1053" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1357" fillId="0" borderId="1054" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1358" fillId="0" borderId="1055" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1359" fillId="0" borderId="1056" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1360" fillId="0" borderId="1057" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1361" fillId="0" borderId="1058" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1362" fillId="0" borderId="1059" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1363" fillId="0" borderId="1060" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1364" fillId="0" borderId="1061" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1365" fillId="0" borderId="1062" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1366" fillId="0" borderId="1063" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1367" fillId="0" borderId="1064" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1368" fillId="0" borderId="1065" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1369" fillId="0" borderId="1066" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1370" fillId="0" borderId="1067" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1371" fillId="0" borderId="1068" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1372" fillId="0" borderId="1069" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1373" fillId="0" borderId="1070" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1374" fillId="0" borderId="1071" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1375" fillId="0" borderId="1072" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1376" fillId="0" borderId="1073" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1377" fillId="0" borderId="1074" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1378" fillId="0" borderId="1075" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1379" fillId="0" borderId="1076" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1380" fillId="0" borderId="1077" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1381" fillId="0" borderId="1078" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1382" fillId="0" borderId="1079" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1383" fillId="0" borderId="1080" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1384" fillId="0" borderId="1081" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1385" fillId="0" borderId="1082" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1386" fillId="0" borderId="1083" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1387" fillId="0" borderId="1084" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1388" fillId="0" borderId="1085" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1389" fillId="0" borderId="1086" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1390" fillId="0" borderId="1087" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1391" fillId="0" borderId="1088" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1392" fillId="0" borderId="1089" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1393" fillId="0" borderId="1090" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1394" fillId="0" borderId="1091" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1395" fillId="0" borderId="1092" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1396" fillId="0" borderId="1093" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1397" fillId="0" borderId="1094" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1398" fillId="0" borderId="1095" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1399" fillId="0" borderId="1096" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1400" fillId="0" borderId="1097" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1401" fillId="0" borderId="1098" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1402" fillId="0" borderId="1099" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1403" fillId="0" borderId="1100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1404" fillId="0" borderId="1101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1406" fillId="0" borderId="1102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1408" fillId="0" borderId="1103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1410" fillId="0" borderId="1104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1412" fillId="0" borderId="1105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1414" fillId="0" borderId="1106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1416" fillId="0" borderId="1107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1418" fillId="0" borderId="1108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1420" fillId="0" borderId="1109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1422" fillId="0" borderId="1110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1424" fillId="0" borderId="1111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1426" fillId="0" borderId="1112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1428" fillId="0" borderId="1113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1430" fillId="0" borderId="1114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1432" fillId="0" borderId="1115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1434" fillId="0" borderId="1116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1436" fillId="0" borderId="1117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1438" fillId="0" borderId="1118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1440" fillId="0" borderId="1119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1442" fillId="0" borderId="1120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1444" fillId="0" borderId="1121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1446" fillId="0" borderId="1122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1448" fillId="0" borderId="1123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1450" fillId="0" borderId="1124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1452" fillId="0" borderId="1125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1454" fillId="0" borderId="1126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1456" fillId="0" borderId="1127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1458" fillId="0" borderId="1128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1460" fillId="0" borderId="1129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1462" fillId="0" borderId="1130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1464" fillId="0" borderId="1131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1466" fillId="0" borderId="1132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1468" fillId="0" borderId="1133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1470" fillId="0" borderId="1134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1472" fillId="0" borderId="1135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1474" fillId="0" borderId="1136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1476" fillId="0" borderId="1137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1478" fillId="0" borderId="1138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1480" fillId="0" borderId="1139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1482" fillId="0" borderId="1140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1484" fillId="0" borderId="1141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1486" fillId="0" borderId="1142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1488" fillId="0" borderId="1143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1490" fillId="0" borderId="1144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1492" fillId="0" borderId="1145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1494" fillId="0" borderId="1146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1496" fillId="0" borderId="1147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1498" fillId="0" borderId="1148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1500" fillId="0" borderId="1149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1502" fillId="0" borderId="1150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1504" fillId="0" borderId="1151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1506" fillId="0" borderId="1152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1508" fillId="0" borderId="1153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1510" fillId="0" borderId="1154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1512" fillId="0" borderId="1155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1514" fillId="0" borderId="1156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1516" fillId="0" borderId="1157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1518" fillId="0" borderId="1158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1520" fillId="0" borderId="1159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1522" fillId="0" borderId="1160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1524" fillId="0" borderId="1161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1526" fillId="0" borderId="1162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1528" fillId="0" borderId="1163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1530" fillId="0" borderId="1164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1532" fillId="0" borderId="1165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1534" fillId="0" borderId="1166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1536" fillId="0" borderId="1167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1538" fillId="0" borderId="1168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1540" fillId="0" borderId="1169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1542" fillId="0" borderId="1170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1544" fillId="0" borderId="1171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1546" fillId="0" borderId="1172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1548" fillId="0" borderId="1173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1550" fillId="0" borderId="1174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1552" fillId="0" borderId="1175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1554" fillId="0" borderId="1176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1556" fillId="0" borderId="1177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1558" fillId="0" borderId="1178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1560" fillId="0" borderId="1179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1562" fillId="0" borderId="1180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1564" fillId="0" borderId="1181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -15054,272 +19769,272 @@
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.7109375" style="609" customWidth="true"/>
-    <col min="3" max="3" width="5.11328125" style="610" customWidth="true"/>
-    <col min="6" max="6" width="5.11328125" style="611" customWidth="true"/>
-    <col min="4" max="4" width="11.11328125" style="612" customWidth="true"/>
-    <col min="7" max="7" width="11.11328125" style="613" customWidth="true"/>
-    <col min="5" max="5" width="7.7109375" style="614" customWidth="true"/>
-    <col min="8" max="8" width="7.7109375" style="615" customWidth="true"/>
+    <col min="2" max="2" width="14.7109375" style="896" customWidth="true"/>
+    <col min="3" max="3" width="5.11328125" style="897" customWidth="true"/>
+    <col min="6" max="6" width="5.11328125" style="898" customWidth="true"/>
+    <col min="4" max="4" width="11.11328125" style="899" customWidth="true"/>
+    <col min="7" max="7" width="11.11328125" style="900" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="901" customWidth="true"/>
+    <col min="8" max="8" width="7.7109375" style="902" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="608" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="815" t="s">
+    <row r="1" s="895" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="1102" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="816" t="s">
+      <c r="B1" s="1103" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="817" t="s">
+      <c r="C1" s="1104" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="818" t="s">
+      <c r="D1" s="1105" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="819" t="s">
+      <c r="E1" s="1106" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="820" t="s">
+      <c r="F1" s="1107" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="821" t="s">
+      <c r="G1" s="1108" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="822" t="s">
+      <c r="H1" s="1109" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="823" t="s">
+      <c r="A2" s="1110" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="824" t="s">
+      <c r="B2" s="1111" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="825" t="s">
+      <c r="C2" s="1112" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="826" t="s">
+      <c r="D2" s="1113" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="827" t="s">
+      <c r="E2" s="1114" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="828" t="s">
+      <c r="F2" s="1115" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="829" t="s">
+      <c r="G2" s="1116" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="830" t="s">
+      <c r="H2" s="1117" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="831" t="s">
+      <c r="A3" s="1118" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="832" t="s">
+      <c r="B3" s="1119" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="833" t="s">
+      <c r="C3" s="1120" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="834" t="s">
+      <c r="D3" s="1121" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="835" t="s">
+      <c r="E3" s="1122" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="836" t="s">
+      <c r="F3" s="1123" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="837" t="s">
+      <c r="G3" s="1124" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="838" t="s">
+      <c r="H3" s="1125" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="839" t="s">
+      <c r="A4" s="1126" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="840" t="s">
+      <c r="B4" s="1127" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="841" t="s">
+      <c r="C4" s="1128" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="842" t="s">
+      <c r="D4" s="1129" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="843" t="s">
+      <c r="E4" s="1130" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="844" t="s">
+      <c r="F4" s="1131" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="845" t="s">
+      <c r="G4" s="1132" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="846" t="s">
+      <c r="H4" s="1133" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="847" t="s">
+      <c r="A5" s="1134" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="848" t="s">
+      <c r="B5" s="1135" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="849" t="s">
+      <c r="C5" s="1136" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="850" t="s">
+      <c r="D5" s="1137" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="851" t="s">
+      <c r="E5" s="1138" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="852" t="s">
+      <c r="F5" s="1139" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="853" t="s">
+      <c r="G5" s="1140" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="854" t="s">
+      <c r="H5" s="1141" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="855" t="s">
+      <c r="A6" s="1142" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="856" t="s">
+      <c r="B6" s="1143" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="857" t="s">
+      <c r="C6" s="1144" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="858" t="s">
+      <c r="D6" s="1145" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="859" t="s">
+      <c r="E6" s="1146" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="860" t="s">
+      <c r="F6" s="1147" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="861" t="s">
+      <c r="G6" s="1148" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="862" t="s">
+      <c r="H6" s="1149" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="863" t="s">
+      <c r="A7" s="1150" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="864" t="s">
+      <c r="B7" s="1151" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="865" t="s">
+      <c r="C7" s="1152" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="866" t="s">
+      <c r="D7" s="1153" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="867" t="s">
+      <c r="E7" s="1154" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="868" t="s">
+      <c r="F7" s="1155" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="869" t="s">
+      <c r="G7" s="1156" t="s">
         <v>1</v>
       </c>
-      <c r="H7" s="870" t="s">
+      <c r="H7" s="1157" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="871" t="s">
+      <c r="A8" s="1158" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="872" t="s">
+      <c r="B8" s="1159" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="873" t="s">
+      <c r="C8" s="1160" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="874" t="s">
+      <c r="D8" s="1161" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="875" t="s">
+      <c r="E8" s="1162" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="876" t="s">
+      <c r="F8" s="1163" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="877" t="s">
+      <c r="G8" s="1164" t="s">
         <v>1</v>
       </c>
-      <c r="H8" s="878" t="s">
+      <c r="H8" s="1165" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="879" t="s">
+      <c r="A9" s="1166" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="880" t="s">
+      <c r="B9" s="1167" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="881" t="s">
+      <c r="C9" s="1168" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="882" t="s">
+      <c r="D9" s="1169" t="s">
         <v>1</v>
       </c>
-      <c r="E9" s="883" t="s">
+      <c r="E9" s="1170" t="s">
         <v>1</v>
       </c>
-      <c r="F9" s="884" t="s">
+      <c r="F9" s="1171" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="885" t="s">
+      <c r="G9" s="1172" t="s">
         <v>1</v>
       </c>
-      <c r="H9" s="886" t="s">
+      <c r="H9" s="1173" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="887" t="s">
+      <c r="A10" s="1174" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="888" t="s">
+      <c r="B10" s="1175" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="889" t="s">
+      <c r="C10" s="1176" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="890" t="s">
+      <c r="D10" s="1177" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="891" t="s">
+      <c r="E10" s="1178" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="892" t="s">
+      <c r="F10" s="1179" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="893" t="s">
+      <c r="G10" s="1180" t="s">
         <v>1</v>
       </c>
-      <c r="H10" s="894" t="s">
+      <c r="H10" s="1181" t="s">
         <v>1</v>
       </c>
     </row>

--- a/tabtools/demo/regtab.xlsx
+++ b/tabtools/demo/regtab.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="330" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="410" uniqueCount="46">
   <si>
     <t>Table 2. OLS Regression</t>
   </si>
@@ -158,1593 +158,3223 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1565">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
+  <fonts count="1945">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -6886,7 +8516,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1182">
+  <borders count="1469">
     <border>
       <left/>
       <right/>
@@ -14957,11 +16587,1972 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1182">
+  <cellXfs count="1469">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -19582,6 +23173,1130 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="1564" fillId="0" borderId="1181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1182" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1183" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1184" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1185" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1186" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1187" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1188" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1189" xfId="0"/>
+    <xf numFmtId="0" fontId="1565" fillId="0" borderId="1190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1566" fillId="0" borderId="1191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1567" fillId="0" borderId="1192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1568" fillId="0" borderId="1193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1569" fillId="0" borderId="1194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1570" fillId="0" borderId="1195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1572" fillId="0" borderId="1196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1574" fillId="0" borderId="1197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1576" fillId="0" borderId="1198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1577" fillId="0" borderId="1199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1578" fillId="0" borderId="1200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1579" fillId="0" borderId="1201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1580" fillId="0" borderId="1202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1581" fillId="0" borderId="1203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1582" fillId="0" borderId="1204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1583" fillId="0" borderId="1205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1584" fillId="0" borderId="1206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1585" fillId="0" borderId="1207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1586" fillId="0" borderId="1208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1587" fillId="0" borderId="1209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1588" fillId="0" borderId="1210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1589" fillId="0" borderId="1211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1590" fillId="0" borderId="1212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1591" fillId="0" borderId="1213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1592" fillId="0" borderId="1214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1593" fillId="0" borderId="1215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1594" fillId="0" borderId="1216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1596" fillId="0" borderId="1217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1598" fillId="0" borderId="1218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1600" fillId="0" borderId="1219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1601" fillId="0" borderId="1220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1602" fillId="0" borderId="1221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1603" fillId="0" borderId="1222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1604" fillId="0" borderId="1223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1605" fillId="0" borderId="1224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1606" fillId="0" borderId="1225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1607" fillId="0" borderId="1226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1608" fillId="0" borderId="1227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1609" fillId="0" borderId="1228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1610" fillId="0" borderId="1229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1611" fillId="0" borderId="1230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1612" fillId="0" borderId="1231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1613" fillId="0" borderId="1232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1614" fillId="0" borderId="1233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1615" fillId="0" borderId="1234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1616" fillId="0" borderId="1235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1617" fillId="0" borderId="1236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1618" fillId="0" borderId="1237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1619" fillId="0" borderId="1238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1620" fillId="0" borderId="1239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1621" fillId="0" borderId="1240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1622" fillId="0" borderId="1241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1623" fillId="0" borderId="1242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1624" fillId="0" borderId="1243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1625" fillId="0" borderId="1244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1626" fillId="0" borderId="1245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1627" fillId="0" borderId="1246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1628" fillId="0" borderId="1247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1630" fillId="0" borderId="1248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1632" fillId="0" borderId="1249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1634" fillId="0" borderId="1250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1636" fillId="0" borderId="1251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1638" fillId="0" borderId="1252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1640" fillId="0" borderId="1253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1642" fillId="0" borderId="1254" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1644" fillId="0" borderId="1255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1645" fillId="0" borderId="1256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1646" fillId="0" borderId="1257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1647" fillId="0" borderId="1258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1648" fillId="0" borderId="1259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1649" fillId="0" borderId="1260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1650" fillId="0" borderId="1261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1651" fillId="0" borderId="1262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1652" fillId="0" borderId="1263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1653" fillId="0" borderId="1264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1654" fillId="0" borderId="1265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1655" fillId="0" borderId="1266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1656" fillId="0" borderId="1267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1657" fillId="0" borderId="1268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1658" fillId="0" borderId="1269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1659" fillId="0" borderId="1270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1660" fillId="0" borderId="1271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1661" fillId="0" borderId="1272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1662" fillId="0" borderId="1273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1663" fillId="0" borderId="1274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1664" fillId="0" borderId="1275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1665" fillId="0" borderId="1276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1666" fillId="0" borderId="1277" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1668" fillId="0" borderId="1278" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1670" fillId="0" borderId="1279" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1672" fillId="0" borderId="1280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1674" fillId="0" borderId="1281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1676" fillId="0" borderId="1282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1678" fillId="0" borderId="1283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1680" fillId="0" borderId="1284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1681" fillId="0" borderId="1285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1682" fillId="0" borderId="1286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1683" fillId="0" borderId="1287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1684" fillId="0" borderId="1288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1685" fillId="0" borderId="1289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1686" fillId="0" borderId="1290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1687" fillId="0" borderId="1291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1688" fillId="0" borderId="1292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1689" fillId="0" borderId="1293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1690" fillId="0" borderId="1294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1691" fillId="0" borderId="1295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1692" fillId="0" borderId="1296" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1693" fillId="0" borderId="1297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1694" fillId="0" borderId="1298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1695" fillId="0" borderId="1299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1696" fillId="0" borderId="1300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1697" fillId="0" borderId="1301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1698" fillId="0" borderId="1302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1699" fillId="0" borderId="1303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1700" fillId="0" borderId="1304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1701" fillId="0" borderId="1305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1702" fillId="0" borderId="1306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1703" fillId="0" borderId="1307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1704" fillId="0" borderId="1308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1705" fillId="0" borderId="1309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1706" fillId="0" borderId="1310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1707" fillId="0" borderId="1311" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1708" fillId="0" borderId="1312" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1709" fillId="0" borderId="1313" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1710" fillId="0" borderId="1314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1711" fillId="0" borderId="1315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1712" fillId="0" borderId="1316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1713" fillId="0" borderId="1317" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1714" fillId="0" borderId="1318" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1715" fillId="0" borderId="1319" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1716" fillId="0" borderId="1320" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1717" fillId="0" borderId="1321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1718" fillId="0" borderId="1322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1719" fillId="0" borderId="1323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1720" fillId="0" borderId="1324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1721" fillId="0" borderId="1325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1722" fillId="0" borderId="1326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1723" fillId="0" borderId="1327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1724" fillId="0" borderId="1328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1725" fillId="0" borderId="1329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1726" fillId="0" borderId="1330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1727" fillId="0" borderId="1331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1728" fillId="0" borderId="1332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1729" fillId="0" borderId="1333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1730" fillId="0" borderId="1334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1731" fillId="0" borderId="1335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1732" fillId="0" borderId="1336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1733" fillId="0" borderId="1337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1734" fillId="0" borderId="1338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1735" fillId="0" borderId="1339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1736" fillId="0" borderId="1340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1737" fillId="0" borderId="1341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1738" fillId="0" borderId="1342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1739" fillId="0" borderId="1343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1740" fillId="0" borderId="1344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1741" fillId="0" borderId="1345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1742" fillId="0" borderId="1346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1743" fillId="0" borderId="1347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1744" fillId="0" borderId="1348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1745" fillId="0" borderId="1349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1746" fillId="0" borderId="1350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1747" fillId="0" borderId="1351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1748" fillId="0" borderId="1352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1749" fillId="0" borderId="1353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1750" fillId="0" borderId="1354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1751" fillId="0" borderId="1355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1752" fillId="0" borderId="1356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1753" fillId="0" borderId="1357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1754" fillId="0" borderId="1358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1755" fillId="0" borderId="1359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1756" fillId="0" borderId="1360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1757" fillId="0" borderId="1361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1758" fillId="0" borderId="1362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1759" fillId="0" borderId="1363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1760" fillId="0" borderId="1364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1761" fillId="0" borderId="1365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1762" fillId="0" borderId="1366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1763" fillId="0" borderId="1367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1764" fillId="0" borderId="1368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1765" fillId="0" borderId="1369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1766" fillId="0" borderId="1370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1767" fillId="0" borderId="1371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1768" fillId="0" borderId="1372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1769" fillId="0" borderId="1373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1770" fillId="0" borderId="1374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1771" fillId="0" borderId="1375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1772" fillId="0" borderId="1376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1773" fillId="0" borderId="1377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1774" fillId="0" borderId="1378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1775" fillId="0" borderId="1379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1776" fillId="0" borderId="1380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1777" fillId="0" borderId="1381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1778" fillId="0" borderId="1382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1779" fillId="0" borderId="1383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1780" fillId="0" borderId="1384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1781" fillId="0" borderId="1385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1782" fillId="0" borderId="1386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1783" fillId="0" borderId="1387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1784" fillId="0" borderId="1388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1786" fillId="0" borderId="1389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1788" fillId="0" borderId="1390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1790" fillId="0" borderId="1391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1792" fillId="0" borderId="1392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1794" fillId="0" borderId="1393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1796" fillId="0" borderId="1394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1798" fillId="0" borderId="1395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1800" fillId="0" borderId="1396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1802" fillId="0" borderId="1397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1804" fillId="0" borderId="1398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1806" fillId="0" borderId="1399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1808" fillId="0" borderId="1400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1810" fillId="0" borderId="1401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1812" fillId="0" borderId="1402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1814" fillId="0" borderId="1403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1816" fillId="0" borderId="1404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1818" fillId="0" borderId="1405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1820" fillId="0" borderId="1406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1822" fillId="0" borderId="1407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1824" fillId="0" borderId="1408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1826" fillId="0" borderId="1409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1828" fillId="0" borderId="1410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1830" fillId="0" borderId="1411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1832" fillId="0" borderId="1412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1834" fillId="0" borderId="1413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1836" fillId="0" borderId="1414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1838" fillId="0" borderId="1415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1840" fillId="0" borderId="1416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1842" fillId="0" borderId="1417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1844" fillId="0" borderId="1418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1846" fillId="0" borderId="1419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1848" fillId="0" borderId="1420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1850" fillId="0" borderId="1421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1852" fillId="0" borderId="1422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1854" fillId="0" borderId="1423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1856" fillId="0" borderId="1424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1858" fillId="0" borderId="1425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1860" fillId="0" borderId="1426" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1862" fillId="0" borderId="1427" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1864" fillId="0" borderId="1428" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1866" fillId="0" borderId="1429" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1868" fillId="0" borderId="1430" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1870" fillId="0" borderId="1431" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1872" fillId="0" borderId="1432" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1874" fillId="0" borderId="1433" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1876" fillId="0" borderId="1434" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1878" fillId="0" borderId="1435" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1880" fillId="0" borderId="1436" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1882" fillId="0" borderId="1437" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1884" fillId="0" borderId="1438" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1886" fillId="0" borderId="1439" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1888" fillId="0" borderId="1440" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1890" fillId="0" borderId="1441" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1892" fillId="0" borderId="1442" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1894" fillId="0" borderId="1443" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1896" fillId="0" borderId="1444" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1898" fillId="0" borderId="1445" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1900" fillId="0" borderId="1446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1902" fillId="0" borderId="1447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1904" fillId="0" borderId="1448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1906" fillId="0" borderId="1449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1908" fillId="0" borderId="1450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1910" fillId="0" borderId="1451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1912" fillId="0" borderId="1452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1914" fillId="0" borderId="1453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1916" fillId="0" borderId="1454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1918" fillId="0" borderId="1455" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1920" fillId="0" borderId="1456" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1922" fillId="0" borderId="1457" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1924" fillId="0" borderId="1458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1926" fillId="0" borderId="1459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1928" fillId="0" borderId="1460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1930" fillId="0" borderId="1461" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1932" fillId="0" borderId="1462" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1934" fillId="0" borderId="1463" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1936" fillId="0" borderId="1464" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1938" fillId="0" borderId="1465" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1940" fillId="0" borderId="1466" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1942" fillId="0" borderId="1467" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1944" fillId="0" borderId="1468" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -19769,272 +24484,272 @@
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.7109375" style="896" customWidth="true"/>
-    <col min="3" max="3" width="5.11328125" style="897" customWidth="true"/>
-    <col min="6" max="6" width="5.11328125" style="898" customWidth="true"/>
-    <col min="4" max="4" width="11.11328125" style="899" customWidth="true"/>
-    <col min="7" max="7" width="11.11328125" style="900" customWidth="true"/>
-    <col min="5" max="5" width="7.7109375" style="901" customWidth="true"/>
-    <col min="8" max="8" width="7.7109375" style="902" customWidth="true"/>
+    <col min="2" max="2" width="14.7109375" style="1183" customWidth="true"/>
+    <col min="3" max="3" width="5.11328125" style="1184" customWidth="true"/>
+    <col min="6" max="6" width="5.11328125" style="1185" customWidth="true"/>
+    <col min="4" max="4" width="11.11328125" style="1186" customWidth="true"/>
+    <col min="7" max="7" width="11.11328125" style="1187" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="1188" customWidth="true"/>
+    <col min="8" max="8" width="7.7109375" style="1189" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="895" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="1102" t="s">
+    <row r="1" s="1182" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="1389" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1103" t="s">
+      <c r="B1" s="1390" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1104" t="s">
+      <c r="C1" s="1391" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1105" t="s">
+      <c r="D1" s="1392" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1106" t="s">
+      <c r="E1" s="1393" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1107" t="s">
+      <c r="F1" s="1394" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="1108" t="s">
+      <c r="G1" s="1395" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1109" t="s">
+      <c r="H1" s="1396" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1110" t="s">
+      <c r="A2" s="1397" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1111" t="s">
+      <c r="B2" s="1398" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1112" t="s">
+      <c r="C2" s="1399" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="1113" t="s">
+      <c r="D2" s="1400" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="1114" t="s">
+      <c r="E2" s="1401" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="1115" t="s">
+      <c r="F2" s="1402" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="1116" t="s">
+      <c r="G2" s="1403" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="1117" t="s">
+      <c r="H2" s="1404" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1118" t="s">
+      <c r="A3" s="1405" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1119" t="s">
+      <c r="B3" s="1406" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1120" t="s">
+      <c r="C3" s="1407" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="1121" t="s">
+      <c r="D3" s="1408" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1122" t="s">
+      <c r="E3" s="1409" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="1123" t="s">
+      <c r="F3" s="1410" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="1124" t="s">
+      <c r="G3" s="1411" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="1125" t="s">
+      <c r="H3" s="1412" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1126" t="s">
+      <c r="A4" s="1413" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="1127" t="s">
+      <c r="B4" s="1414" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="1128" t="s">
+      <c r="C4" s="1415" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="1129" t="s">
+      <c r="D4" s="1416" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="1130" t="s">
+      <c r="E4" s="1417" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="1131" t="s">
+      <c r="F4" s="1418" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="1132" t="s">
+      <c r="G4" s="1419" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="1133" t="s">
+      <c r="H4" s="1420" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1134" t="s">
+      <c r="A5" s="1421" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="1135" t="s">
+      <c r="B5" s="1422" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="1136" t="s">
+      <c r="C5" s="1423" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="1137" t="s">
+      <c r="D5" s="1424" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="1138" t="s">
+      <c r="E5" s="1425" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="1139" t="s">
+      <c r="F5" s="1426" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="1140" t="s">
+      <c r="G5" s="1427" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="1141" t="s">
+      <c r="H5" s="1428" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1142" t="s">
+      <c r="A6" s="1429" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="1143" t="s">
+      <c r="B6" s="1430" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="1144" t="s">
+      <c r="C6" s="1431" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="1145" t="s">
+      <c r="D6" s="1432" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="1146" t="s">
+      <c r="E6" s="1433" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="1147" t="s">
+      <c r="F6" s="1434" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="1148" t="s">
+      <c r="G6" s="1435" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="1149" t="s">
+      <c r="H6" s="1436" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1150" t="s">
+      <c r="A7" s="1437" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="1151" t="s">
+      <c r="B7" s="1438" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="1152" t="s">
+      <c r="C7" s="1439" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="1153" t="s">
+      <c r="D7" s="1440" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="1154" t="s">
+      <c r="E7" s="1441" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="1155" t="s">
+      <c r="F7" s="1442" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="1156" t="s">
+      <c r="G7" s="1443" t="s">
         <v>1</v>
       </c>
-      <c r="H7" s="1157" t="s">
+      <c r="H7" s="1444" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1158" t="s">
+      <c r="A8" s="1445" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="1159" t="s">
+      <c r="B8" s="1446" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="1160" t="s">
+      <c r="C8" s="1447" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="1161" t="s">
+      <c r="D8" s="1448" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="1162" t="s">
+      <c r="E8" s="1449" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="1163" t="s">
+      <c r="F8" s="1450" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="1164" t="s">
+      <c r="G8" s="1451" t="s">
         <v>1</v>
       </c>
-      <c r="H8" s="1165" t="s">
+      <c r="H8" s="1452" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1166" t="s">
+      <c r="A9" s="1453" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="1167" t="s">
+      <c r="B9" s="1454" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="1168" t="s">
+      <c r="C9" s="1455" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="1169" t="s">
+      <c r="D9" s="1456" t="s">
         <v>1</v>
       </c>
-      <c r="E9" s="1170" t="s">
+      <c r="E9" s="1457" t="s">
         <v>1</v>
       </c>
-      <c r="F9" s="1171" t="s">
+      <c r="F9" s="1458" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="1172" t="s">
+      <c r="G9" s="1459" t="s">
         <v>1</v>
       </c>
-      <c r="H9" s="1173" t="s">
+      <c r="H9" s="1460" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1174" t="s">
+      <c r="A10" s="1461" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="1175" t="s">
+      <c r="B10" s="1462" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="1176" t="s">
+      <c r="C10" s="1463" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="1177" t="s">
+      <c r="D10" s="1464" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="1178" t="s">
+      <c r="E10" s="1465" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="1179" t="s">
+      <c r="F10" s="1466" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="1180" t="s">
+      <c r="G10" s="1467" t="s">
         <v>1</v>
       </c>
-      <c r="H10" s="1181" t="s">
+      <c r="H10" s="1468" t="s">
         <v>1</v>
       </c>
     </row>
